--- a/Src/Data/Tables/CharacterDefine.xlsx
+++ b/Src/Data/Tables/CharacterDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="84">
   <si>
     <t>TypeID</t>
   </si>
@@ -98,6 +98,12 @@
     <t>角色高度</t>
   </si>
   <si>
+    <t>击杀掉落</t>
+  </si>
+  <si>
+    <t>击杀掉落数量</t>
+  </si>
+  <si>
     <t>Integer</t>
   </si>
   <si>
@@ -177,6 +183,12 @@
   </si>
   <si>
     <t>Height</t>
+  </si>
+  <si>
+    <t>KillDrop</t>
+  </si>
+  <si>
+    <t>KillDropCount</t>
   </si>
   <si>
     <t>战士</t>
@@ -1013,13 +1025,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1089,7 +1101,7 @@
     <cellStyle name="好 2" xfId="59"/>
     <cellStyle name="适中 2" xfId="60"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill patternType="none"/>
@@ -1171,6 +1183,21 @@
         <patternFill patternType="none"/>
       </fill>
       <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1431,17 +1458,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:Y11" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:Y11" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:AA11" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:AA11" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="27">
     <tableColumn id="1" name="Key" dataDxfId="0"/>
     <tableColumn id="3" name="TID" dataDxfId="1"/>
     <tableColumn id="5" name="Name" dataDxfId="2"/>
@@ -1449,24 +1469,26 @@
     <tableColumn id="9" name="Class" dataDxfId="4"/>
     <tableColumn id="2" name="Resource" dataDxfId="5"/>
     <tableColumn id="98" name="Description" dataDxfId="6"/>
-    <tableColumn id="24" name="AI"/>
-    <tableColumn id="7" name="InitLevel" dataDxfId="7"/>
-    <tableColumn id="6" name="Speed" dataDxfId="8"/>
-    <tableColumn id="8" name="MaxHP" dataDxfId="9"/>
-    <tableColumn id="10" name="MaxMP" dataDxfId="10"/>
-    <tableColumn id="11" name="GrowthSTR" dataDxfId="11"/>
-    <tableColumn id="12" name="GrowthINT" dataDxfId="12"/>
-    <tableColumn id="13" name="GrowthDEX" dataDxfId="13"/>
-    <tableColumn id="14" name="STR" dataDxfId="14"/>
-    <tableColumn id="15" name="INT" dataDxfId="15"/>
-    <tableColumn id="16" name="DEX" dataDxfId="16"/>
-    <tableColumn id="17" name="AD" dataDxfId="17"/>
-    <tableColumn id="18" name="AP" dataDxfId="18"/>
-    <tableColumn id="19" name="DEF" dataDxfId="19"/>
-    <tableColumn id="20" name="MDEF" dataDxfId="20"/>
-    <tableColumn id="21" name="SPD" dataDxfId="21"/>
-    <tableColumn id="22" name="CRI" dataDxfId="22"/>
-    <tableColumn id="23" name="Height" dataDxfId="23"/>
+    <tableColumn id="24" name="AI" dataDxfId="7"/>
+    <tableColumn id="7" name="InitLevel" dataDxfId="8"/>
+    <tableColumn id="6" name="Speed" dataDxfId="9"/>
+    <tableColumn id="8" name="MaxHP" dataDxfId="10"/>
+    <tableColumn id="10" name="MaxMP" dataDxfId="11"/>
+    <tableColumn id="11" name="GrowthSTR" dataDxfId="12"/>
+    <tableColumn id="12" name="GrowthINT" dataDxfId="13"/>
+    <tableColumn id="13" name="GrowthDEX" dataDxfId="14"/>
+    <tableColumn id="14" name="STR" dataDxfId="15"/>
+    <tableColumn id="15" name="INT" dataDxfId="16"/>
+    <tableColumn id="16" name="DEX" dataDxfId="17"/>
+    <tableColumn id="17" name="AD" dataDxfId="18"/>
+    <tableColumn id="18" name="AP" dataDxfId="19"/>
+    <tableColumn id="19" name="DEF" dataDxfId="20"/>
+    <tableColumn id="20" name="MDEF" dataDxfId="21"/>
+    <tableColumn id="21" name="SPD" dataDxfId="22"/>
+    <tableColumn id="22" name="CRI" dataDxfId="23"/>
+    <tableColumn id="23" name="Height" dataDxfId="24"/>
+    <tableColumn id="25" name="KillDrop"/>
+    <tableColumn id="26" name="KillDropCount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1759,7 +1781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultColWidth="16.287037037037" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="11" style="2" customWidth="1"/>
@@ -1770,7 +1792,7 @@
     <col min="10" max="16384" width="16.287037037037" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:27">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1842,159 +1864,177 @@
       <c r="Y1" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="Z1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="2:25">
+    <row r="2" spans="1:27">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="AA2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:27">
       <c r="A3" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="L3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="M3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="N3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="O3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="P3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="Q3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="R3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="S3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="T3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="U3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="V3" s="6" t="s">
         <v>48</v>
       </c>
+      <c r="W3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="Y3" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.2" spans="1:25">
+    <row r="4" s="1" customFormat="1" ht="13.2" spans="1:27">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2002,21 +2042,21 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="7"/>
       <c r="I4" s="1">
         <v>1</v>
       </c>
@@ -2069,7 +2109,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.2" spans="1:25">
+    <row r="5" s="1" customFormat="1" ht="13.2" spans="1:27">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2077,21 +2117,21 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="7"/>
       <c r="I5" s="1">
         <v>1</v>
       </c>
@@ -2144,7 +2184,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="13.2" spans="1:25">
+    <row r="6" s="1" customFormat="1" ht="13.2" spans="1:27">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2152,22 +2192,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6">
+        <v>65</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7">
         <v>1</v>
       </c>
       <c r="J6" s="1">
@@ -2219,7 +2259,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:27">
       <c r="A7" s="1">
         <v>1001</v>
       </c>
@@ -2227,31 +2267,31 @@
         <v>1001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="6">
+        <v>56</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="7">
         <v>1</v>
       </c>
       <c r="J7" s="1">
         <v>300</v>
       </c>
       <c r="K7" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L7" s="4">
         <v>250</v>
@@ -2295,8 +2335,14 @@
       <c r="Y7" s="4">
         <v>1.8</v>
       </c>
+      <c r="Z7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:27">
       <c r="A8" s="1">
         <v>1002</v>
       </c>
@@ -2304,31 +2350,31 @@
         <v>1002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="6">
+        <v>56</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="7">
         <v>1</v>
       </c>
       <c r="J8" s="1">
         <v>300</v>
       </c>
       <c r="K8" s="4">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="L8" s="4">
         <v>500</v>
@@ -2372,8 +2418,14 @@
       <c r="Y8" s="4">
         <v>2.5</v>
       </c>
+      <c r="Z8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:27">
       <c r="A9" s="1">
         <v>1003</v>
       </c>
@@ -2381,31 +2433,31 @@
         <v>1003</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <v>1</v>
       </c>
       <c r="J9" s="1">
         <v>300</v>
       </c>
       <c r="K9" s="4">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="L9" s="4">
         <v>1000</v>
@@ -2449,8 +2501,14 @@
       <c r="Y9" s="9">
         <v>2</v>
       </c>
+      <c r="Z9" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:27">
       <c r="A10" s="1">
         <v>1004</v>
       </c>
@@ -2458,31 +2516,31 @@
         <v>1004</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="6">
+        <v>64</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="7">
         <v>1</v>
       </c>
       <c r="J10" s="4">
         <v>300</v>
       </c>
       <c r="K10" s="4">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="L10" s="4">
         <v>1000</v>
@@ -2526,8 +2584,14 @@
       <c r="Y10" s="4">
         <v>1.5</v>
       </c>
+      <c r="Z10" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:27">
       <c r="A11" s="1">
         <v>1005</v>
       </c>
@@ -2535,31 +2599,31 @@
         <v>1005</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="6">
+        <v>60</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="7">
         <v>1</v>
       </c>
       <c r="J11" s="4">
         <v>300</v>
       </c>
       <c r="K11" s="4">
-        <v>20000</v>
+        <v>500</v>
       </c>
       <c r="L11" s="4">
         <v>10000</v>
@@ -2601,6 +2665,12 @@
         <v>0.05</v>
       </c>
       <c r="Y11" s="9">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA11" s="4">
         <v>2</v>
       </c>
     </row>
